--- a/reports/集团总公司_利润表_2026-09.xlsx
+++ b/reports/集团总公司_利润表_2026-09.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>237457698</v>
+        <v>257937934</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>180650801</v>
+        <v>195276789</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1540607409</v>
+        <v>1673204578</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>735836</v>
+        <v>954819</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6381480</v>
+        <v>8259727</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>639520</v>
+        <v>836160</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5535840</v>
+        <v>7228854</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>540051</v>
+        <v>705937</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4691138</v>
+        <v>6103049</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>496625</v>
+        <v>651240</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4316703</v>
+        <v>5633675</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>270886</v>
+        <v>357707</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2346007</v>
+        <v>3098187</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>216547</v>
+        <v>281391</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1876440</v>
+        <v>2440547</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>234558233</v>
+        <v>254150680</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>177751336</v>
+        <v>191489535</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>74111949</v>
+        <v>82517410</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>750864297</v>
+        <v>826044897</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1675921</v>
+        <v>2963717</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14543057</v>
+        <v>25789806</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1510440</v>
+        <v>2155337</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>13137302</v>
+        <v>18754632</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>98647237</v>
+        <v>102474617</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>721241658</v>
+        <v>758024156</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1736429</v>
+        <v>2162213</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>15010849</v>
+        <v>18759877</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>755093</v>
+        <v>1083104</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>6567525</v>
+        <v>9382894</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2696989</v>
+        <v>3255985</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>23463618</v>
+        <v>28157765</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1192664</v>
+        <v>1628123</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>10322160</v>
+        <v>14080357</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>56629963</v>
+        <v>56739748</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>479585686</v>
+        <v>479967175</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>176934</v>
+        <v>175638</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1581587</v>
+        <v>1576852</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3449482</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>29857244</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2296277</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>19901833</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>176309682</v>
+        <v>198148729</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>142439394</v>
+        <v>149320031</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>113035854</v>
+        <v>120126017</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>953934738</v>
+        <v>1019913882</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>29403540</v>
+        <v>29194014</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>254220061</v>
+        <v>254082050</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5708196</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>49699689</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1827831</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>15903772</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1143852</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>9940909</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1374908</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>11931492</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1032996</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>8950958</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>689728</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5968946</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>575382</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4975319</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3181356</v>
+        <v>3203070</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>27676227</v>
+        <v>27698072</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1500569</v>
+        <v>1510987</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>13044519</v>
+        <v>13052530</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3910639</v>
+        <v>3893227</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>33783944</v>
+        <v>33789189</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>25236675</v>
+        <v>25161383</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>228412429</v>
+        <v>228554456</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>369883</v>
+        <v>3067732</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3267132</v>
+        <v>26728342</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1171735</v>
+        <v>1150393</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>10424679</v>
+        <v>10378954</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1220011</v>
+        <v>1099493</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>10797788</v>
+        <v>9915975</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>126023</v>
+        <v>123096</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1117850</v>
+        <v>1111717</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>489297</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4418672</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>999733</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>8697443</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>326882</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2946452</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>245577</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2210401</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>410011</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3685089</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1437182</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>12435740</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>219213</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1966365</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>164459</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1474952</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>273975</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2458244</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>191571</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1720555</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136621</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1228690</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>109105</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>982676</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81694</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>736790</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>58248551</v>
+        <v>59476840</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>63391847</v>
+        <v>63421035</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>570881</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4969904</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136038</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1227499</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>220216</v>
+        <v>215912</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1955347</v>
+        <v>1945832</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>58028335</v>
+        <v>59831809</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7472078</v>
+        <v>7323707</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>66145646</v>
+        <v>65821899</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50556257</v>
+        <v>52508102</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50556257</v>
+        <v>52508102</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50556257</v>
+        <v>52508102</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50556257</v>
+        <v>52508102</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50556257</v>
+        <v>52508102</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
